--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_biobio.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_biobio.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:44</t>
+    <t xml:space="preserve">2026-09-09 20:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_biobio.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_biobio.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:04</t>
+    <t xml:space="preserve">2026-09-18 17:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_biobio.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_biobio.xlsx
@@ -30,105 +30,105 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Negrete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rosendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucapel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yumbel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Juana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Biobío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Alamos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabrero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Bárbara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curanilahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Angeles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contulmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirúa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lebu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulchén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilleco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talcahuano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nacimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cañete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coronel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiguayante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concepción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualpén</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Pedro de la Paz</t>
   </si>
   <si>
-    <t xml:space="preserve">Hualpén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concepción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiguayante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coronel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualqui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cañete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nacimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talcahuano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilleco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mulchén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lebu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirúa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contulmo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Angeles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curanilahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Bárbara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabrero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Alamos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alto Biobío</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Juana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yumbel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tucapel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rosendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negrete</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:04</t>
+    <t xml:space="preserve">2026-09-27 21:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -558,13 +558,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>133237</v>
+        <v>11015</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>148070</v>
+        <v>10474</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>89.98</v>
+        <v>105.17</v>
       </c>
     </row>
     <row r="3">
@@ -572,13 +572,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>87876</v>
+        <v>3695</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>97536</v>
+        <v>3595</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>90.1</v>
+        <v>102.78</v>
       </c>
     </row>
     <row r="4">
@@ -586,13 +586,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>220235</v>
+        <v>4431</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>238661</v>
+        <v>4312</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>92.28</v>
+        <v>102.76</v>
       </c>
     </row>
     <row r="5">
@@ -600,13 +600,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>85494</v>
+        <v>15469</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>91435</v>
+        <v>15273</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>93.5</v>
+        <v>101.28</v>
       </c>
     </row>
     <row r="6">
@@ -614,13 +614,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>119010</v>
+        <v>22433</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>126729</v>
+        <v>22158</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>93.91</v>
+        <v>101.24</v>
       </c>
     </row>
     <row r="7">
@@ -628,13 +628,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>24882</v>
+        <v>14971</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>26366</v>
+        <v>14819</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>94.37</v>
+        <v>101.03</v>
       </c>
     </row>
     <row r="8">
@@ -642,13 +642,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>35194</v>
+        <v>6838</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>37139</v>
+        <v>6789</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>94.76</v>
+        <v>100.72</v>
       </c>
     </row>
     <row r="9">
@@ -656,13 +656,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>26673</v>
+        <v>22775</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>27981</v>
+        <v>22647</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>95.33</v>
+        <v>100.57</v>
       </c>
     </row>
     <row r="10">
@@ -670,13 +670,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>151061</v>
+        <v>4198</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>158347</v>
+        <v>4186</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>95.4</v>
+        <v>100.29</v>
       </c>
     </row>
     <row r="11">
@@ -684,13 +684,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>9627</v>
+        <v>30734</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>10023</v>
+        <v>30842</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>96.05</v>
+        <v>99.65</v>
       </c>
     </row>
     <row r="12">
@@ -698,13 +698,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>29881</v>
+        <v>45295</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>31078</v>
+        <v>45672</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>96.15</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="13">
@@ -712,13 +712,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>37316</v>
+        <v>23683</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>38769</v>
+        <v>23896</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>96.25</v>
+        <v>99.11</v>
       </c>
     </row>
     <row r="14">
@@ -726,13 +726,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>48133</v>
+        <v>14477</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>49975</v>
+        <v>14625</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>96.31</v>
+        <v>98.99</v>
       </c>
     </row>
     <row r="15">
@@ -740,13 +740,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>26143</v>
+        <v>33482</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>27128</v>
+        <v>33921</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>96.37</v>
+        <v>98.71</v>
       </c>
     </row>
     <row r="16">
@@ -754,13 +754,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>56746</v>
+        <v>215759</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>58873</v>
+        <v>220030</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>96.39</v>
+        <v>98.06</v>
       </c>
     </row>
     <row r="17">
@@ -768,13 +768,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>11462</v>
+        <v>6169</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>11855</v>
+        <v>6340</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>96.68</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="18">
@@ -796,13 +796,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>6169</v>
+        <v>11462</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6340</v>
+        <v>11855</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>97.3</v>
+        <v>96.68</v>
       </c>
     </row>
     <row r="20">
@@ -810,13 +810,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>215759</v>
+        <v>56746</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>220030</v>
+        <v>58873</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>98.06</v>
+        <v>96.39</v>
       </c>
     </row>
     <row r="21">
@@ -824,13 +824,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>33482</v>
+        <v>26143</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>33921</v>
+        <v>27128</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>98.71</v>
+        <v>96.37</v>
       </c>
     </row>
     <row r="22">
@@ -838,13 +838,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>14477</v>
+        <v>48133</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>14625</v>
+        <v>49975</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>98.99</v>
+        <v>96.31</v>
       </c>
     </row>
     <row r="23">
@@ -852,13 +852,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>23683</v>
+        <v>37316</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>23896</v>
+        <v>38769</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>99.11</v>
+        <v>96.25</v>
       </c>
     </row>
     <row r="24">
@@ -866,13 +866,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45295</v>
+        <v>29881</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>45672</v>
+        <v>31078</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>99.17</v>
+        <v>96.15</v>
       </c>
     </row>
     <row r="25">
@@ -880,13 +880,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>30734</v>
+        <v>9627</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>30842</v>
+        <v>10023</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>99.65</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="26">
@@ -894,13 +894,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4198</v>
+        <v>151061</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>4186</v>
+        <v>158347</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>100.29</v>
+        <v>95.4</v>
       </c>
     </row>
     <row r="27">
@@ -908,13 +908,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>22775</v>
+        <v>26673</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>22647</v>
+        <v>27981</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>100.57</v>
+        <v>95.33</v>
       </c>
     </row>
     <row r="28">
@@ -922,13 +922,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>6838</v>
+        <v>35194</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>6789</v>
+        <v>37139</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>100.72</v>
+        <v>94.76</v>
       </c>
     </row>
     <row r="29">
@@ -936,13 +936,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>14971</v>
+        <v>24882</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>14819</v>
+        <v>26366</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>101.03</v>
+        <v>94.37</v>
       </c>
     </row>
     <row r="30">
@@ -950,13 +950,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>22433</v>
+        <v>119010</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>22158</v>
+        <v>126729</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>101.24</v>
+        <v>93.91</v>
       </c>
     </row>
     <row r="31">
@@ -964,13 +964,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>15469</v>
+        <v>85494</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>15273</v>
+        <v>91435</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>101.28</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="32">
@@ -978,13 +978,13 @@
         <v>34</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>4431</v>
+        <v>220235</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>4312</v>
+        <v>238661</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>102.76</v>
+        <v>92.28</v>
       </c>
     </row>
     <row r="33">
@@ -992,13 +992,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>3695</v>
+        <v>87876</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>3595</v>
+        <v>97536</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>102.78</v>
+        <v>90.1</v>
       </c>
     </row>
     <row r="34">
@@ -1006,13 +1006,13 @@
         <v>36</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>11015</v>
+        <v>133237</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>10474</v>
+        <v>148070</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>105.17</v>
+        <v>89.98</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_biobio.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2021_biobio.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Alto Biobío</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Quilaco</t>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Contulmo</t>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:49</t>
+    <t xml:space="preserve">2026-10-05 05:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
